--- a/requirements/ ontoFotovoltaica_requirements.xlsx
+++ b/requirements/ ontoFotovoltaica_requirements.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
   <si>
     <t>Identifier</t>
   </si>
@@ -68,21 +68,51 @@
     <t>¿Dispone el edificio de sistemas de generación de energía renovable (placas solares, geotermia, biomasa)?</t>
   </si>
   <si>
+    <t>Deprecated</t>
+  </si>
+  <si>
+    <t>Versión simplificada sugerida en FOT012</t>
+  </si>
+  <si>
+    <t>FOT02</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <strike/>
+        <color theme="1"/>
+      </rPr>
+      <t>¿Cuál es la energía generada (en un intervalo de tiempo) por todas las instalaciones fotovoltaicas asociadas a un elemento de infraestructura o división administrativa (expresada en kWh)?</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+      </rPr>
+      <t>Sugerencia simplificada: ¿Cuál es la energía generada por el conjunto de instalaciones fotovoltaicas asociadas a un elemento de infraestructura?</t>
+    </r>
+  </si>
+  <si>
+    <t>Actualizado en FOT13</t>
+  </si>
+  <si>
+    <t>FOT03</t>
+  </si>
+  <si>
+    <t>¿Cuál es la energía generada por cada instalación fotovoltaica de una división adeministrativa durante un periodo de tiempo?</t>
+  </si>
+  <si>
     <t>Proposed</t>
   </si>
   <si>
-    <t>FOT02</t>
-  </si>
-  <si>
-    <t>¿Cuál es la energía generada (en un intervalo de tiempo) por todas las instalaciones fotovoltaicas asociadas a un elemento de infraestructura o división administrativa (expresada en kWh)?</t>
-  </si>
-  <si>
-    <t>FOT03</t>
-  </si>
-  <si>
-    <t>¿Cuál es la energía generada por cada instalación fotovoltaica de una división adeministrativa durante un periodo de tiempo?</t>
-  </si>
-  <si>
     <t>¿Energía media para KPI?</t>
   </si>
   <si>
@@ -92,20 +122,78 @@
     <t>¿Cuál es la energía generada por las intalaciones fotovoltaicas de un elemento de infraestructura en cada estación del año?</t>
   </si>
   <si>
+    <t xml:space="preserve">La ontologia no modela estaciones de año como tal, </t>
+  </si>
+  <si>
     <t>FOT05</t>
   </si>
   <si>
     <t>¿Cuál es la relación entre la producción fotovoltaica y el consumo energético del elemento de infraestructura o división administrativa (expresada como porcentaje del consumo cubierto?</t>
   </si>
   <si>
-    <t>¿Para KPI?</t>
+    <t>¿Para KPI? 
+Esta pregunta solo es válida si se integra la ontologia de suministros con la ontologia de fotovoltaica, ¿no?</t>
+  </si>
+  <si>
+    <t>FOT06</t>
+  </si>
+  <si>
+    <t>¿Qué medidor fotovoltaico ha realizado cada observación de generación registrada?</t>
+  </si>
+  <si>
+    <t>FOT07</t>
+  </si>
+  <si>
+    <t>¿A qué instalación fotovoltaica corresponde cada observación de generación?</t>
+  </si>
+  <si>
+    <t>FOT08</t>
+  </si>
+  <si>
+    <t>¿Cual es el estado operativo de la instalación fotovoltaica?</t>
+  </si>
+  <si>
+    <t>FOT09</t>
+  </si>
+  <si>
+    <t>¿Cuál es el tipo de uso asociado a la instalación fotovoltaica?</t>
+  </si>
+  <si>
+    <t>FOT10</t>
+  </si>
+  <si>
+    <t>¿Quien es el fabricante del medidor fotovoltaico?</t>
+  </si>
+  <si>
+    <t>FOT11</t>
+  </si>
+  <si>
+    <t>¿Cuál es el periodo temporal asociado a cada observación de generación fotovoltaica?</t>
+  </si>
+  <si>
+    <t>FOT12</t>
+  </si>
+  <si>
+    <t>¿Dispone el elemento de infraestructura/edificio de una o varias instalaciones fotovoltaicas asociadas?</t>
+  </si>
+  <si>
+    <t>Otra versión de la FOT01</t>
+  </si>
+  <si>
+    <t>FOT13</t>
+  </si>
+  <si>
+    <t>Sugerencia simplificada: ¿Cuál es la energía generada por el conjunto de instalaciones fotovoltaicas asociadas a un elemento de infraestructura?</t>
+  </si>
+  <si>
+    <t>Simplificación de FOT02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -114,6 +202,11 @@
     </font>
     <font>
       <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -138,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -150,6 +243,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -378,7 +474,7 @@
     <col customWidth="1" min="1" max="1" width="13.63"/>
     <col customWidth="1" min="2" max="2" width="9.88"/>
     <col customWidth="1" min="3" max="3" width="6.63"/>
-    <col customWidth="1" min="4" max="4" width="63.38"/>
+    <col customWidth="1" min="4" max="4" width="67.0"/>
     <col customWidth="1" min="5" max="5" width="17.63"/>
     <col customWidth="1" min="7" max="7" width="25.63"/>
     <col customWidth="1" min="8" max="8" width="32.13"/>
@@ -457,11 +553,13 @@
         <v>17</v>
       </c>
       <c r="G2" s="1"/>
-      <c r="H2" s="2"/>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>14</v>
@@ -470,17 +568,19 @@
         <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3" s="2"/>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>14</v>
@@ -489,19 +589,19 @@
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>14</v>
@@ -510,15 +610,18 @@
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="H5" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>14</v>
@@ -527,56 +630,172 @@
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K6" s="1"/>
     </row>
     <row r="7">
-      <c r="D7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="H7" s="2"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8">
-      <c r="D8" s="2"/>
+      <c r="A8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9">
-      <c r="D9" s="2"/>
+      <c r="A9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10">
-      <c r="D10" s="2"/>
+      <c r="A10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="H10" s="2"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11">
-      <c r="D11" s="2"/>
+      <c r="A11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="H11" s="2"/>
       <c r="M11" s="1"/>
     </row>
     <row r="12">
-      <c r="D12" s="1"/>
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="2"/>
     </row>
     <row r="13">
-      <c r="D13" s="1"/>
+      <c r="A13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="H13" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="14">
-      <c r="D14" s="1"/>
+      <c r="A14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="H14" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="15">
       <c r="D15" s="1"/>
@@ -594,33 +813,33 @@
       <c r="H17" s="2"/>
     </row>
     <row r="18">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7"/>
     </row>
     <row r="19">
       <c r="D19" s="1"/>
